--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/7mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/7mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.57225680556</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>715.6013046519125</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>712.1263486527164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+        <v>0.239478788</v>
+      </c>
+      <c r="Y2">
+        <v>0.260982172</v>
+      </c>
+      <c r="Z2">
+        <v>0.3542058497594112</v>
+      </c>
+      <c r="AA2">
+        <v>10.75169200000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.0344284774179214</v>
+      </c>
+      <c r="AC2">
+        <v>24.63706335744346</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.572373125</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>712.5476775437874</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>712.1522479382535</v>
+      </c>
+      <c r="X3">
+        <v>0.239518756</v>
+      </c>
+      <c r="Y3">
+        <v>0.26096594</v>
+      </c>
+      <c r="Z3">
+        <v>0.3542209145658556</v>
+      </c>
+      <c r="AA3">
+        <v>10.723592</v>
+      </c>
+      <c r="AB3">
+        <v>0.03451243603446057</v>
+      </c>
+      <c r="AC3">
+        <v>24.5917561427334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.57248944444</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>714.039657567562</v>
       </c>
-      <c r="V4">
-        <v>1.526946000075502</v>
-      </c>
-      <c r="W4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.239502896</v>
+      </c>
+      <c r="Y4">
+        <v>0.260951938</v>
+      </c>
+      <c r="Z4">
+        <v>0.3541998745600324</v>
+      </c>
+      <c r="AA4">
+        <v>10.724521</v>
+      </c>
+      <c r="AB4">
+        <v>0.03450781975354786</v>
+      </c>
+      <c r="AC4">
+        <v>24.63995180022647</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.57260518518</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>710.0107539732907</v>
       </c>
-      <c r="V5">
-        <v>2.036911459613011</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>24.64700720281429</v>
+      </c>
+      <c r="X5">
+        <v>0.239552064</v>
+      </c>
+      <c r="Y5">
+        <v>0.2609478</v>
+      </c>
+      <c r="Z5">
+        <v>0.3542300745158436</v>
+      </c>
+      <c r="AA5">
+        <v>10.697868</v>
+      </c>
+      <c r="AB5">
+        <v>0.03458928435081218</v>
+      </c>
+      <c r="AC5">
+        <v>24.5587638613167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.57272092593</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>709.9195417227045</v>
       </c>
-      <c r="V6">
-        <v>2.352861322646534</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.239572048</v>
+      </c>
+      <c r="Y6">
+        <v>0.260938252</v>
+      </c>
+      <c r="Z6">
+        <v>0.3542365559054144</v>
+      </c>
+      <c r="AA6">
+        <v>10.68310200000001</v>
+      </c>
+      <c r="AB6">
+        <v>0.03463368046228525</v>
+      </c>
+      <c r="AC6">
+        <v>24.58712656195613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.57283724537</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>709.3644123636121</v>
       </c>
-      <c r="V7">
-        <v>0.3498203720922865</v>
-      </c>
-      <c r="W7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0.239545402</v>
+      </c>
+      <c r="Y7">
+        <v>0.260933478</v>
+      </c>
+      <c r="Z7">
+        <v>0.3542150188240443</v>
+      </c>
+      <c r="AA7">
+        <v>10.694038</v>
+      </c>
+      <c r="AB7">
+        <v>0.03459928925359346</v>
+      </c>
+      <c r="AC7">
+        <v>24.54350448957397</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.57295298611</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>708.6154491701687</v>
       </c>
-      <c r="V8">
-        <v>0.6544427471823862</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>0.239614872</v>
+      </c>
+      <c r="Y8">
+        <v>0.260932842</v>
+      </c>
+      <c r="Z8">
+        <v>0.3542615346291118</v>
+      </c>
+      <c r="AA8">
+        <v>10.65898499999999</v>
+      </c>
+      <c r="AB8">
+        <v>0.03470776044434989</v>
+      </c>
+      <c r="AC8">
+        <v>24.59445525696362</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.57306930555</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>707.6449703656418</v>
       </c>
-      <c r="V9">
-        <v>0.8620958724287658</v>
-      </c>
-      <c r="W9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.239619948</v>
+      </c>
+      <c r="Y9">
+        <v>0.260921384</v>
+      </c>
+      <c r="Z9">
+        <v>0.354256528673782</v>
+      </c>
+      <c r="AA9">
+        <v>10.650718</v>
+      </c>
+      <c r="AB9">
+        <v>0.03473201464632676</v>
+      </c>
+      <c r="AC9">
+        <v>24.57793547513894</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.573185625</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>711.9968933903975</v>
       </c>
-      <c r="V10">
-        <v>2.284557876189383</v>
-      </c>
-      <c r="W10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.239592984</v>
+      </c>
+      <c r="Y10">
+        <v>0.26092234</v>
+      </c>
+      <c r="Z10">
+        <v>0.3542389948793044</v>
+      </c>
+      <c r="AA10">
+        <v>10.664678</v>
+      </c>
+      <c r="AB10">
+        <v>0.03468874744518434</v>
+      </c>
+      <c r="AC10">
+        <v>24.69828041657534</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.57330136574</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>709.3820815262246</v>
       </c>
-      <c r="V11">
-        <v>2.190663152359729</v>
-      </c>
-      <c r="W11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>0.239615824</v>
+      </c>
+      <c r="Y11">
+        <v>0.260916928</v>
+      </c>
+      <c r="Z11">
+        <v>0.354250457202466</v>
+      </c>
+      <c r="AA11">
+        <v>10.650552</v>
+      </c>
+      <c r="AB11">
+        <v>0.03473196518367493</v>
+      </c>
+      <c r="AC11">
+        <v>24.63823375749168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.57341768518</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>710.5160034424382</v>
       </c>
-      <c r="V12">
-        <v>1.311237013603097</v>
-      </c>
-      <c r="W12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.239587908</v>
+      </c>
+      <c r="Y12">
+        <v>0.260910882</v>
+      </c>
+      <c r="Z12">
+        <v>0.3542271220641277</v>
+      </c>
+      <c r="AA12">
+        <v>10.661487</v>
+      </c>
+      <c r="AB12">
+        <v>0.03469720077479111</v>
+      </c>
+      <c r="AC12">
+        <v>24.65291642514445</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.57353342592</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>708.178134892062</v>
       </c>
-      <c r="V13">
-        <v>1.169109046013196</v>
-      </c>
-      <c r="W13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.239572048</v>
+      </c>
+      <c r="Y13">
+        <v>0.260902288</v>
+      </c>
+      <c r="Z13">
+        <v>0.3542100648860069</v>
+      </c>
+      <c r="AA13">
+        <v>10.66512</v>
+      </c>
+      <c r="AB13">
+        <v>0.03468483189183769</v>
+      </c>
+      <c r="AC13">
+        <v>24.56303955820632</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.57364974537</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>711.4265158959558</v>
       </c>
-      <c r="V14">
-        <v>1.675641242097498</v>
-      </c>
-      <c r="W14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.239527004</v>
+      </c>
+      <c r="Y14">
+        <v>0.260895924</v>
+      </c>
+      <c r="Z14">
+        <v>0.3541749127267906</v>
+      </c>
+      <c r="AA14">
+        <v>10.68445999999999</v>
+      </c>
+      <c r="AB14">
+        <v>0.03462412191361711</v>
+      </c>
+      <c r="AC14">
+        <v>24.63251841896143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.57376548611</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>711.2094939150242</v>
       </c>
-      <c r="V15">
-        <v>1.816049522670973</v>
-      </c>
-      <c r="W15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>0.239494648</v>
+      </c>
+      <c r="Y15">
+        <v>0.260901334</v>
+      </c>
+      <c r="Z15">
+        <v>0.3541570167363954</v>
+      </c>
+      <c r="AA15">
+        <v>10.703343</v>
+      </c>
+      <c r="AB15">
+        <v>0.03456653646697667</v>
+      </c>
+      <c r="AC15">
+        <v>24.5840489070737</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.57388180555</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>712.8018636993834</v>
       </c>
-      <c r="V16">
-        <v>0.863550968457196</v>
-      </c>
-      <c r="W16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>0.239514316</v>
+      </c>
+      <c r="Y16">
+        <v>0.260904516</v>
+      </c>
+      <c r="Z16">
+        <v>0.3541726613364478</v>
+      </c>
+      <c r="AA16">
+        <v>10.6951</v>
+      </c>
+      <c r="AB16">
+        <v>0.03459234924396309</v>
+      </c>
+      <c r="AC16">
+        <v>24.65749101083684</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.57399754629</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>711.6697311057181</v>
       </c>
-      <c r="V17">
-        <v>0.8194697484223923</v>
-      </c>
-      <c r="W17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>0.23952288</v>
+      </c>
+      <c r="Y17">
+        <v>0.260886058</v>
+      </c>
+      <c r="Z17">
+        <v>0.354164856108386</v>
+      </c>
+      <c r="AA17">
+        <v>10.681589</v>
+      </c>
+      <c r="AB17">
+        <v>0.03463175062053293</v>
+      </c>
+      <c r="AC17">
+        <v>24.64636865183496</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.57411386574</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>715.4925626060303</v>
       </c>
-      <c r="V18">
-        <v>1.963654140272163</v>
-      </c>
-      <c r="W18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>0.239424864</v>
+      </c>
+      <c r="Y18">
+        <v>0.26089306</v>
+      </c>
+      <c r="Z18">
+        <v>0.3541037337526704</v>
+      </c>
+      <c r="AA18">
+        <v>10.734098</v>
+      </c>
+      <c r="AB18">
+        <v>0.03447104680774861</v>
+      </c>
+      <c r="AC18">
+        <v>24.66377761618847</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.57422960648</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>715.8875113078034</v>
       </c>
-      <c r="V19">
-        <v>2.32950978354931</v>
-      </c>
-      <c r="W19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>0.239400122</v>
+      </c>
+      <c r="Y19">
+        <v>0.26089115</v>
+      </c>
+      <c r="Z19">
+        <v>0.3540855977894856</v>
+      </c>
+      <c r="AA19">
+        <v>10.745514</v>
+      </c>
+      <c r="AB19">
+        <v>0.03443589333236667</v>
+      </c>
+      <c r="AC19">
+        <v>24.65222597736896</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.57434592592</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>713.9709094233555</v>
       </c>
-      <c r="V20">
-        <v>1.011992726327948</v>
-      </c>
-      <c r="W20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>0.239405514</v>
+      </c>
+      <c r="Y20">
+        <v>0.260889558</v>
+      </c>
+      <c r="Z20">
+        <v>0.3540880704105118</v>
+      </c>
+      <c r="AA20">
+        <v>10.742022</v>
+      </c>
+      <c r="AB20">
+        <v>0.03444636409849629</v>
+      </c>
+      <c r="AC20">
+        <v>24.59370190173142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.57446166666</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>717.3045793901715</v>
       </c>
-      <c r="V21">
-        <v>1.673061075851958</v>
-      </c>
-      <c r="W21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>0.239398852</v>
+      </c>
+      <c r="Y21">
+        <v>0.260885102</v>
+      </c>
+      <c r="Z21">
+        <v>0.3540802829648501</v>
+      </c>
+      <c r="AA21">
+        <v>10.743125</v>
+      </c>
+      <c r="AB21">
+        <v>0.03444243189928971</v>
+      </c>
+      <c r="AC21">
+        <v>24.70571412669463</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.57457798611</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>715.2509783275129</v>
       </c>
-      <c r="V22">
-        <v>1.681725759034097</v>
-      </c>
-      <c r="W22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>0.239427718</v>
+      </c>
+      <c r="Y22">
+        <v>0.260884466</v>
+      </c>
+      <c r="Z22">
+        <v>0.3540993317514066</v>
+      </c>
+      <c r="AA22">
+        <v>10.728374</v>
+      </c>
+      <c r="AB22">
+        <v>0.03448749834077742</v>
+      </c>
+      <c r="AC22">
+        <v>24.66721692830953</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.57469372685</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>713.9923497164709</v>
       </c>
-      <c r="V23">
-        <v>1.671939428549304</v>
-      </c>
-      <c r="W23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>0.239454364</v>
+      </c>
+      <c r="Y23">
+        <v>0.26088192</v>
+      </c>
+      <c r="Z23">
+        <v>0.3541154735697536</v>
+      </c>
+      <c r="AA23">
+        <v>10.713778</v>
+      </c>
+      <c r="AB23">
+        <v>0.03453197690440722</v>
+      </c>
+      <c r="AC23">
+        <v>24.65556733033262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.5748100463</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>710.9369241304152</v>
       </c>
-      <c r="V24">
-        <v>2.218514334261797</v>
-      </c>
-      <c r="W24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>0.239484816</v>
+      </c>
+      <c r="Y24">
+        <v>0.260872372</v>
+      </c>
+      <c r="Z24">
+        <v>0.3541290323702086</v>
+      </c>
+      <c r="AA24">
+        <v>10.693778</v>
+      </c>
+      <c r="AB24">
+        <v>0.03459236263707952</v>
+      </c>
+      <c r="AC24">
+        <v>24.59298789160921</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.57492578703</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>714.5152332433286</v>
       </c>
-      <c r="V25">
-        <v>1.932758339874998</v>
-      </c>
-      <c r="W25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>0.23945817</v>
+      </c>
+      <c r="Y25">
+        <v>0.26087842</v>
+      </c>
+      <c r="Z25">
+        <v>0.3541154687406995</v>
+      </c>
+      <c r="AA25">
+        <v>10.71012500000001</v>
+      </c>
+      <c r="AB25">
+        <v>0.03454276704371763</v>
+      </c>
+      <c r="AC25">
+        <v>24.68133325111187</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.57504152778</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>715.3480287309852</v>
       </c>
-      <c r="V26">
-        <v>2.343632800767051</v>
-      </c>
-      <c r="W26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>0.239470224</v>
+      </c>
+      <c r="Y26">
+        <v>0.26087651</v>
+      </c>
+      <c r="Z26">
+        <v>0.3541222128762757</v>
+      </c>
+      <c r="AA26">
+        <v>10.703143</v>
+      </c>
+      <c r="AB26">
+        <v>0.03456401563534425</v>
+      </c>
+      <c r="AC26">
+        <v>24.72530044977046</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.57515726852</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>711.3773515042739</v>
       </c>
-      <c r="V27">
-        <v>2.093885056192367</v>
-      </c>
-      <c r="W27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23">
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>0.239474348</v>
+      </c>
+      <c r="Y27">
+        <v>0.260883194</v>
+      </c>
+      <c r="Z27">
+        <v>0.3541299256793567</v>
+      </c>
+      <c r="AA27">
+        <v>10.704423</v>
+      </c>
+      <c r="AB27">
+        <v>0.03456091826321305</v>
+      </c>
+      <c r="AC27">
+        <v>24.58585449964019</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.57527358797</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>711.5395088791456</v>
       </c>
-      <c r="V28">
-        <v>2.247123943874294</v>
-      </c>
-      <c r="W28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23">
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>0.239494648</v>
+      </c>
+      <c r="Y28">
+        <v>0.260870464</v>
+      </c>
+      <c r="Z28">
+        <v>0.3541342759578903</v>
+      </c>
+      <c r="AA28">
+        <v>10.687908</v>
+      </c>
+      <c r="AB28">
+        <v>0.03461024380871117</v>
+      </c>
+      <c r="AC28">
+        <v>24.62655588183784</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.5753899074</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>713.4938987061324</v>
       </c>
-      <c r="V29">
-        <v>1.177971891836509</v>
-      </c>
-      <c r="W29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23">
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="X29">
+        <v>0.239507338</v>
+      </c>
+      <c r="Y29">
+        <v>0.260873328</v>
+      </c>
+      <c r="Z29">
+        <v>0.3541449677994054</v>
+      </c>
+      <c r="AA29">
+        <v>10.682995</v>
+      </c>
+      <c r="AB29">
+        <v>0.03462579039799865</v>
+      </c>
+      <c r="AC29">
+        <v>24.70529018684942</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.57550564815</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>711.7676831535886</v>
       </c>
-      <c r="V30">
-        <v>1.068606821144777</v>
-      </c>
-      <c r="W30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23">
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <v>0.239503214</v>
+      </c>
+      <c r="Y30">
+        <v>0.260857732</v>
+      </c>
+      <c r="Z30">
+        <v>0.3541306903679963</v>
+      </c>
+      <c r="AA30">
+        <v>10.677259</v>
+      </c>
+      <c r="AB30">
+        <v>0.03464156057656982</v>
+      </c>
+      <c r="AC30">
+        <v>24.65674331240979</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.57562196759</v>
       </c>
@@ -2618,14 +3104,29 @@
       <c r="U31">
         <v>713.4067577047498</v>
       </c>
-      <c r="V31">
-        <v>0.9724521472564454</v>
-      </c>
-      <c r="W31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23">
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>0.239532396</v>
+      </c>
+      <c r="Y31">
+        <v>0.26087301</v>
+      </c>
+      <c r="Z31">
+        <v>0.3541616807052407</v>
+      </c>
+      <c r="AA31">
+        <v>10.67030699999999</v>
+      </c>
+      <c r="AB31">
+        <v>0.0346650311746729</v>
+      </c>
+      <c r="AC31">
+        <v>24.73026749605747</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" s="1">
         <v>46068.57573828704</v>
       </c>
@@ -2689,14 +3190,29 @@
       <c r="U32">
         <v>709.9699467982398</v>
       </c>
-      <c r="V32">
-        <v>1.719015735564287</v>
-      </c>
-      <c r="W32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23">
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>0.239535886</v>
+      </c>
+      <c r="Y32">
+        <v>0.260866962</v>
+      </c>
+      <c r="Z32">
+        <v>0.3541595862671437</v>
+      </c>
+      <c r="AA32">
+        <v>10.665538</v>
+      </c>
+      <c r="AB32">
+        <v>0.03467905367408727</v>
+      </c>
+      <c r="AC32">
+        <v>24.62108589200504</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="1">
         <v>46068.57585460648</v>
       </c>
@@ -2760,14 +3276,29 @@
       <c r="U33">
         <v>713.1181060059773</v>
       </c>
-      <c r="V33">
-        <v>1.906388182207619</v>
-      </c>
-      <c r="W33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23">
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>0.239523514</v>
+      </c>
+      <c r="Y33">
+        <v>0.260860278</v>
+      </c>
+      <c r="Z33">
+        <v>0.3541462951904841</v>
+      </c>
+      <c r="AA33">
+        <v>10.66838199999999</v>
+      </c>
+      <c r="AB33">
+        <v>0.03466938477457726</v>
+      </c>
+      <c r="AC33">
+        <v>24.723366006839</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="1">
         <v>46068.57597034722</v>
       </c>
@@ -2831,14 +3362,29 @@
       <c r="U34">
         <v>711.5554301755509</v>
       </c>
-      <c r="V34">
-        <v>1.5740933733414</v>
-      </c>
-      <c r="W34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23">
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>0.239504164</v>
+      </c>
+      <c r="Y34">
+        <v>0.260855824</v>
+      </c>
+      <c r="Z34">
+        <v>0.3541299274109121</v>
+      </c>
+      <c r="AA34">
+        <v>10.67583</v>
+      </c>
+      <c r="AB34">
+        <v>0.03464574268281786</v>
+      </c>
+      <c r="AC34">
+        <v>24.65236633842391</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" s="1">
         <v>46068.57608666667</v>
       </c>
@@ -2902,14 +3448,29 @@
       <c r="U35">
         <v>710.9643511160251</v>
       </c>
-      <c r="V35">
-        <v>1.112803541480909</v>
-      </c>
-      <c r="W35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23">
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>0.239515584</v>
+      </c>
+      <c r="Y35">
+        <v>0.260853914</v>
+      </c>
+      <c r="Z35">
+        <v>0.3541362441603237</v>
+      </c>
+      <c r="AA35">
+        <v>10.669165</v>
+      </c>
+      <c r="AB35">
+        <v>0.03466615009317017</v>
+      </c>
+      <c r="AC35">
+        <v>24.64639690668146</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" s="1">
         <v>46068.57620240741</v>
       </c>
@@ -2973,14 +3534,29 @@
       <c r="U36">
         <v>711.0711893586833</v>
       </c>
-      <c r="V36">
-        <v>0.3149809606461861</v>
-      </c>
-      <c r="W36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23">
+      <c r="V36" t="b">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>0.239521928</v>
+      </c>
+      <c r="Y36">
+        <v>0.26085264</v>
+      </c>
+      <c r="Z36">
+        <v>0.3541395964698197</v>
+      </c>
+      <c r="AA36">
+        <v>10.665356</v>
+      </c>
+      <c r="AB36">
+        <v>0.03467780159361997</v>
+      </c>
+      <c r="AC36">
+        <v>24.6583856235198</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29">
       <c r="A37" s="1">
         <v>46068.57631872685</v>
       </c>
@@ -3044,14 +3620,29 @@
       <c r="U37">
         <v>709.0617689129776</v>
       </c>
-      <c r="V37">
-        <v>1.130560626198304</v>
-      </c>
-      <c r="W37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23">
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+      <c r="X37">
+        <v>0.239569194</v>
+      </c>
+      <c r="Y37">
+        <v>0.260853914</v>
+      </c>
+      <c r="Z37">
+        <v>0.35417250480935</v>
+      </c>
+      <c r="AA37">
+        <v>10.64236</v>
+      </c>
+      <c r="AB37">
+        <v>0.03474946982383632</v>
+      </c>
+      <c r="AC37">
+        <v>24.63952054207752</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
       <c r="A38" s="1">
         <v>46068.5764350463</v>
       </c>
@@ -3115,14 +3706,29 @@
       <c r="U38">
         <v>711.4102008116286</v>
       </c>
-      <c r="V38">
-        <v>1.269372001912866</v>
-      </c>
-      <c r="W38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="X38">
+        <v>0.239525418</v>
+      </c>
+      <c r="Y38">
+        <v>0.260856142</v>
+      </c>
+      <c r="Z38">
+        <v>0.3541445364356182</v>
+      </c>
+      <c r="AA38">
+        <v>10.665362</v>
+      </c>
+      <c r="AB38">
+        <v>0.0346782272098209</v>
+      </c>
+      <c r="AC38">
+        <v>24.67044458312997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
       <c r="A39" s="1">
         <v>46068.57655136574</v>
       </c>
@@ -3186,14 +3792,29 @@
       <c r="U39">
         <v>712.9696737037284</v>
       </c>
-      <c r="V39">
-        <v>1.967181060018003</v>
-      </c>
-      <c r="W39" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
+      <c r="V39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>0.239521612</v>
+      </c>
+      <c r="Y39">
+        <v>0.260859324</v>
+      </c>
+      <c r="Z39">
+        <v>0.3541443060855497</v>
+      </c>
+      <c r="AA39">
+        <v>10.668856</v>
+      </c>
+      <c r="AB39">
+        <v>0.03466779410570477</v>
+      </c>
+      <c r="AC39">
+        <v>24.71708585157237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29">
       <c r="A40" s="1">
         <v>46068.57666710648</v>
       </c>
@@ -3257,14 +3878,29 @@
       <c r="U40">
         <v>712.512475853851</v>
       </c>
-      <c r="V40">
-        <v>0.8016645021275071</v>
-      </c>
-      <c r="W40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23">
+      <c r="V40" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>0.239490208</v>
+      </c>
+      <c r="Y40">
+        <v>0.26086378</v>
+      </c>
+      <c r="Z40">
+        <v>0.3541263495474061</v>
+      </c>
+      <c r="AA40">
+        <v>10.68678600000001</v>
+      </c>
+      <c r="AB40">
+        <v>0.03461286411277181</v>
+      </c>
+      <c r="AC40">
+        <v>24.66209750538395</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
       <c r="A41" s="1">
         <v>46068.57678342592</v>
       </c>
@@ -3328,14 +3964,29 @@
       <c r="U41">
         <v>714.0381153311275</v>
       </c>
-      <c r="V41">
-        <v>0.7829615997089473</v>
-      </c>
-      <c r="W41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>0.239487352</v>
+      </c>
+      <c r="Y41">
+        <v>0.260862824</v>
+      </c>
+      <c r="Z41">
+        <v>0.3541237138532619</v>
+      </c>
+      <c r="AA41">
+        <v>10.687736</v>
+      </c>
+      <c r="AB41">
+        <v>0.0346098082042381</v>
+      </c>
+      <c r="AC41">
+        <v>24.71272222212597</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" s="1">
         <v>46068.57689916667</v>
       </c>
@@ -3399,14 +4050,29 @@
       <c r="U42">
         <v>713.6613870812514</v>
       </c>
-      <c r="V42">
-        <v>0.7947218588205189</v>
-      </c>
-      <c r="W42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="X42">
+        <v>0.239486402</v>
+      </c>
+      <c r="Y42">
+        <v>0.260859324</v>
+      </c>
+      <c r="Z42">
+        <v>0.3541204931384833</v>
+      </c>
+      <c r="AA42">
+        <v>10.686461</v>
+      </c>
+      <c r="AB42">
+        <v>0.03461330425440679</v>
+      </c>
+      <c r="AC42">
+        <v>24.70217872566533</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
       <c r="A43" s="1">
         <v>46068.57701548611</v>
       </c>
@@ -3470,14 +4136,29 @@
       <c r="U43">
         <v>714.1399881961484</v>
       </c>
-      <c r="V43">
-        <v>0.2521115104014111</v>
-      </c>
-      <c r="W43" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="V43" t="b">
+        <v>1</v>
+      </c>
+      <c r="X43">
+        <v>0.239459122</v>
+      </c>
+      <c r="Y43">
+        <v>0.260862824</v>
+      </c>
+      <c r="Z43">
+        <v>0.354104623034303</v>
+      </c>
+      <c r="AA43">
+        <v>10.701851</v>
+      </c>
+      <c r="AB43">
+        <v>0.03456626582659929</v>
+      </c>
+      <c r="AC43">
+        <v>24.68515266939254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
       <c r="A44" s="1">
         <v>46068.57713122686</v>
       </c>
@@ -3541,14 +4222,29 @@
       <c r="U44">
         <v>713.4175940632206</v>
       </c>
-      <c r="V44">
-        <v>0.3675022326706064</v>
-      </c>
-      <c r="W44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
+      <c r="V44" t="b">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>0.239470858</v>
+      </c>
+      <c r="Y44">
+        <v>0.260859006</v>
+      </c>
+      <c r="Z44">
+        <v>0.3541097468900908</v>
+      </c>
+      <c r="AA44">
+        <v>10.69407399999999</v>
+      </c>
+      <c r="AB44">
+        <v>0.03458975879851429</v>
+      </c>
+      <c r="AC44">
+        <v>24.67694250126318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
       <c r="A45" s="1">
         <v>46068.57724754629</v>
       </c>
@@ -3612,14 +4308,29 @@
       <c r="U45">
         <v>711.3589135025504</v>
       </c>
-      <c r="V45">
-        <v>1.44305205412781</v>
-      </c>
-      <c r="W45" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
+      <c r="V45" t="b">
+        <v>1</v>
+      </c>
+      <c r="X45">
+        <v>0.239473078</v>
+      </c>
+      <c r="Y45">
+        <v>0.260832272</v>
+      </c>
+      <c r="Z45">
+        <v>0.3540915548321876</v>
+      </c>
+      <c r="AA45">
+        <v>10.679597</v>
+      </c>
+      <c r="AB45">
+        <v>0.03463110036980979</v>
+      </c>
+      <c r="AC45">
+        <v>24.63514193246566</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29">
       <c r="A46" s="1">
         <v>46068.57736328704</v>
       </c>
@@ -3683,14 +4394,29 @@
       <c r="U46">
         <v>709.9843802714938</v>
       </c>
-      <c r="V46">
-        <v>1.727930563509039</v>
-      </c>
-      <c r="W46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
+      <c r="V46" t="b">
+        <v>1</v>
+      </c>
+      <c r="X46">
+        <v>0.239498138</v>
+      </c>
+      <c r="Y46">
+        <v>0.260836092</v>
+      </c>
+      <c r="Z46">
+        <v>0.3541113172369665</v>
+      </c>
+      <c r="AA46">
+        <v>10.668977</v>
+      </c>
+      <c r="AB46">
+        <v>0.03466447305095573</v>
+      </c>
+      <c r="AC46">
+        <v>24.61123441652071</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
       <c r="A47" s="1">
         <v>46068.57747902778</v>
       </c>
@@ -3754,14 +4480,29 @@
       <c r="U47">
         <v>711.2410314516595</v>
       </c>
-      <c r="V47">
-        <v>0.7618409687285458</v>
-      </c>
-      <c r="W47" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23">
+      <c r="V47" t="b">
+        <v>1</v>
+      </c>
+      <c r="X47">
+        <v>0.23950702</v>
+      </c>
+      <c r="Y47">
+        <v>0.260829408</v>
+      </c>
+      <c r="Z47">
+        <v>0.3541124012328724</v>
+      </c>
+      <c r="AA47">
+        <v>10.661194</v>
+      </c>
+      <c r="AB47">
+        <v>0.03468777125694559</v>
+      </c>
+      <c r="AC47">
+        <v>24.67136620754921</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29">
       <c r="A48" s="1">
         <v>46068.57759534723</v>
       </c>
@@ -3825,14 +4566,29 @@
       <c r="U48">
         <v>712.8726997629461</v>
       </c>
-      <c r="V48">
-        <v>1.448211722053628</v>
-      </c>
-      <c r="W48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23">
+      <c r="V48" t="b">
+        <v>1</v>
+      </c>
+      <c r="X48">
+        <v>0.239492746</v>
+      </c>
+      <c r="Y48">
+        <v>0.260842138</v>
+      </c>
+      <c r="Z48">
+        <v>0.3541121239706875</v>
+      </c>
+      <c r="AA48">
+        <v>10.674696</v>
+      </c>
+      <c r="AB48">
+        <v>0.0346475197338284</v>
+      </c>
+      <c r="AC48">
+        <v>24.69927093274421</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29">
       <c r="A49" s="1">
         <v>46068.57771108796</v>
       </c>
@@ -3896,11 +4652,26 @@
       <c r="U49">
         <v>710.7518865892579</v>
       </c>
-      <c r="V49">
-        <v>1.11051434720967</v>
-      </c>
-      <c r="W49" t="b">
-        <v>1</v>
+      <c r="V49" t="b">
+        <v>1</v>
+      </c>
+      <c r="X49">
+        <v>0.239490524</v>
+      </c>
+      <c r="Y49">
+        <v>0.26083991</v>
+      </c>
+      <c r="Z49">
+        <v>0.3541089800253627</v>
+      </c>
+      <c r="AA49">
+        <v>10.674693</v>
+      </c>
+      <c r="AB49">
+        <v>0.0346472466707188</v>
+      </c>
+      <c r="AC49">
+        <v>24.62559593633677</v>
       </c>
     </row>
   </sheetData>
